--- a/data/rival.xlsx
+++ b/data/rival.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="669" documentId="8_{9713198C-5AF7-4EEE-B6B7-339E279726B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB2115BF-9279-4C40-9B70-A9FEF930607E}"/>
+  <xr:revisionPtr revIDLastSave="686" documentId="8_{9713198C-5AF7-4EEE-B6B7-339E279726B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E6C2CD8-8B70-4904-8521-82F9F2583558}"/>
   <bookViews>
-    <workbookView xWindow="1050" yWindow="1215" windowWidth="13245" windowHeight="14175" xr2:uid="{610C4827-A39E-4D77-86AB-FDE647078AA6}"/>
+    <workbookView xWindow="7740" yWindow="1200" windowWidth="14805" windowHeight="13890" xr2:uid="{610C4827-A39E-4D77-86AB-FDE647078AA6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>player</t>
     <phoneticPr fontId="1"/>
@@ -596,6 +596,10 @@
     <rPh sb="0" eb="3">
       <t>チシキオウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベライボビ・ラッホヤハ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -682,10 +686,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -985,7 +985,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CB0C30-A935-445D-8022-3321E6129271}">
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.875" customWidth="1"/>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="B56">
         <v>1850</v>
@@ -2766,59 +2766,59 @@
         <v>0.75</v>
       </c>
       <c r="E56">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F56">
-        <v>20</v>
+        <v>1680</v>
       </c>
       <c r="G56">
-        <v>1552</v>
+        <v>1679</v>
       </c>
       <c r="H56">
-        <v>651</v>
+        <v>1683</v>
       </c>
       <c r="I56">
-        <v>484</v>
+        <v>1681</v>
       </c>
       <c r="J56">
-        <v>387</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B57">
+        <v>1850</v>
+      </c>
+      <c r="C57">
         <v>1900</v>
       </c>
-      <c r="C57">
-        <v>1950</v>
-      </c>
       <c r="D57">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="E57">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F57">
-        <v>839</v>
+        <v>20</v>
       </c>
       <c r="G57">
-        <v>857</v>
+        <v>1552</v>
       </c>
       <c r="H57">
-        <v>849</v>
+        <v>651</v>
       </c>
       <c r="I57">
-        <v>848</v>
+        <v>484</v>
       </c>
       <c r="J57">
-        <v>859</v>
+        <v>387</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B58">
         <v>1900</v>
@@ -2827,30 +2827,30 @@
         <v>1950</v>
       </c>
       <c r="D58">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="E58">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F58">
-        <v>297</v>
+        <v>839</v>
       </c>
       <c r="G58">
-        <v>296</v>
+        <v>857</v>
       </c>
       <c r="H58">
-        <v>294</v>
+        <v>849</v>
       </c>
       <c r="I58">
-        <v>293</v>
+        <v>848</v>
       </c>
       <c r="J58">
-        <v>295</v>
+        <v>859</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B59">
         <v>1900</v>
@@ -2862,27 +2862,27 @@
         <v>0.75</v>
       </c>
       <c r="E59">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F59">
-        <v>13</v>
+        <v>297</v>
       </c>
       <c r="G59">
-        <v>484</v>
+        <v>296</v>
       </c>
       <c r="H59">
-        <v>659</v>
+        <v>294</v>
       </c>
       <c r="I59">
-        <v>1497</v>
+        <v>293</v>
       </c>
       <c r="J59">
-        <v>14</v>
+        <v>295</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B60">
         <v>1900</v>
@@ -2891,30 +2891,30 @@
         <v>1950</v>
       </c>
       <c r="D60">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="E60">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F60">
-        <v>279</v>
+        <v>13</v>
       </c>
       <c r="G60">
-        <v>389</v>
+        <v>484</v>
       </c>
       <c r="H60">
-        <v>731</v>
+        <v>659</v>
       </c>
       <c r="I60">
-        <v>805</v>
+        <v>1497</v>
       </c>
       <c r="J60">
-        <v>1531</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B61">
         <v>1900</v>
@@ -2926,59 +2926,59 @@
         <v>0.8</v>
       </c>
       <c r="E61">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F61">
-        <v>446</v>
+        <v>279</v>
       </c>
       <c r="G61">
-        <v>611</v>
+        <v>389</v>
       </c>
       <c r="H61">
-        <v>610</v>
+        <v>731</v>
       </c>
       <c r="I61">
-        <v>640</v>
+        <v>805</v>
       </c>
       <c r="J61">
-        <v>600</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="B62">
+        <v>1900</v>
+      </c>
+      <c r="C62">
         <v>1950</v>
       </c>
-      <c r="C62">
-        <v>2000</v>
-      </c>
       <c r="D62">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E62">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F62">
-        <v>1718</v>
+        <v>446</v>
       </c>
       <c r="G62">
-        <v>1695</v>
+        <v>611</v>
       </c>
       <c r="H62">
-        <v>1740</v>
+        <v>610</v>
       </c>
       <c r="I62">
-        <v>1696</v>
+        <v>640</v>
       </c>
       <c r="J62">
-        <v>1737</v>
+        <v>600</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B63">
         <v>1950</v>
@@ -2987,30 +2987,30 @@
         <v>2000</v>
       </c>
       <c r="D63">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="E63">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F63">
-        <v>1290</v>
+        <v>1718</v>
       </c>
       <c r="G63">
-        <v>1385</v>
+        <v>1695</v>
       </c>
       <c r="H63">
-        <v>971</v>
+        <v>1740</v>
       </c>
       <c r="I63">
-        <v>1267</v>
+        <v>1696</v>
       </c>
       <c r="J63">
-        <v>810</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B64">
         <v>1950</v>
@@ -3022,27 +3022,27 @@
         <v>0.8</v>
       </c>
       <c r="E64">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F64">
-        <v>805</v>
+        <v>1290</v>
       </c>
       <c r="G64">
-        <v>1334</v>
+        <v>1385</v>
       </c>
       <c r="H64">
-        <v>1296</v>
+        <v>971</v>
       </c>
       <c r="I64">
-        <v>967</v>
+        <v>1267</v>
       </c>
       <c r="J64">
-        <v>981</v>
+        <v>810</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B65">
         <v>1950</v>
@@ -3051,30 +3051,30 @@
         <v>2000</v>
       </c>
       <c r="D65">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="E65">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F65">
-        <v>988</v>
+        <v>805</v>
       </c>
       <c r="G65">
-        <v>1013</v>
+        <v>1334</v>
       </c>
       <c r="H65">
-        <v>1004</v>
+        <v>1296</v>
       </c>
       <c r="I65">
-        <v>987</v>
+        <v>967</v>
       </c>
       <c r="J65">
-        <v>1014</v>
+        <v>981</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B66">
         <v>1950</v>
@@ -3086,59 +3086,59 @@
         <v>0.85</v>
       </c>
       <c r="E66">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F66">
-        <v>85</v>
+        <v>988</v>
       </c>
       <c r="G66">
-        <v>267</v>
+        <v>1013</v>
       </c>
       <c r="H66">
-        <v>483</v>
+        <v>1004</v>
       </c>
       <c r="I66">
-        <v>274</v>
+        <v>987</v>
       </c>
       <c r="J66">
-        <v>266</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="B67">
+        <v>1950</v>
+      </c>
+      <c r="C67">
         <v>2000</v>
       </c>
-      <c r="C67">
-        <v>2050</v>
-      </c>
       <c r="D67">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="E67">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F67">
-        <v>1742</v>
+        <v>85</v>
       </c>
       <c r="G67">
-        <v>541</v>
+        <v>267</v>
       </c>
       <c r="H67">
-        <v>511</v>
+        <v>483</v>
       </c>
       <c r="I67">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="J67">
-        <v>538</v>
+        <v>266</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="B68">
         <v>2000</v>
@@ -3147,30 +3147,30 @@
         <v>2050</v>
       </c>
       <c r="D68">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="E68">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F68">
-        <v>145</v>
+        <v>1742</v>
       </c>
       <c r="G68">
-        <v>144</v>
+        <v>541</v>
       </c>
       <c r="H68">
-        <v>861</v>
+        <v>511</v>
       </c>
       <c r="I68">
-        <v>410</v>
+        <v>267</v>
       </c>
       <c r="J68">
-        <v>411</v>
+        <v>538</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="B69">
         <v>2000</v>
@@ -3182,27 +3182,27 @@
         <v>0.85</v>
       </c>
       <c r="E69">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F69">
-        <v>513</v>
+        <v>145</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>144</v>
       </c>
       <c r="H69">
-        <v>512</v>
+        <v>861</v>
       </c>
       <c r="I69">
-        <v>515</v>
+        <v>410</v>
       </c>
       <c r="J69">
-        <v>518</v>
+        <v>411</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B70">
         <v>2000</v>
@@ -3217,24 +3217,24 @@
         <v>29</v>
       </c>
       <c r="F70">
-        <v>10001</v>
+        <v>513</v>
       </c>
       <c r="G70">
-        <v>10002</v>
+        <v>1</v>
       </c>
       <c r="H70">
-        <v>10003</v>
+        <v>512</v>
       </c>
       <c r="I70">
-        <v>10004</v>
+        <v>515</v>
       </c>
       <c r="J70">
-        <v>10005</v>
+        <v>518</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B71">
         <v>2000</v>
@@ -3243,30 +3243,30 @@
         <v>2050</v>
       </c>
       <c r="D71">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="E71">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F71">
-        <v>1739</v>
+        <v>10001</v>
       </c>
       <c r="G71">
-        <v>1704</v>
+        <v>10002</v>
       </c>
       <c r="H71">
-        <v>1713</v>
+        <v>10003</v>
       </c>
       <c r="I71">
-        <v>1738</v>
+        <v>10004</v>
       </c>
       <c r="J71">
-        <v>1717</v>
+        <v>10005</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B72">
         <v>2000</v>
@@ -3278,59 +3278,59 @@
         <v>0.9</v>
       </c>
       <c r="E72">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F72">
-        <v>620</v>
+        <v>1739</v>
       </c>
       <c r="G72">
-        <v>1217</v>
+        <v>1704</v>
       </c>
       <c r="H72">
-        <v>328</v>
+        <v>1713</v>
       </c>
       <c r="I72">
-        <v>1190</v>
+        <v>1738</v>
       </c>
       <c r="J72">
-        <v>665</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B73">
+        <v>2000</v>
+      </c>
+      <c r="C73">
         <v>2050</v>
       </c>
-      <c r="C73">
-        <v>2100</v>
-      </c>
       <c r="D73">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="E73">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F73">
-        <v>1554</v>
+        <v>620</v>
       </c>
       <c r="G73">
-        <v>515</v>
+        <v>1217</v>
       </c>
       <c r="H73">
-        <v>1552</v>
+        <v>328</v>
       </c>
       <c r="I73">
-        <v>1343</v>
+        <v>1190</v>
       </c>
       <c r="J73">
-        <v>1551</v>
+        <v>665</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B74">
         <v>2050</v>
@@ -3342,27 +3342,27 @@
         <v>0.85</v>
       </c>
       <c r="E74">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F74">
-        <v>94</v>
+        <v>1554</v>
       </c>
       <c r="G74">
-        <v>78</v>
+        <v>515</v>
       </c>
       <c r="H74">
-        <v>170</v>
+        <v>1552</v>
       </c>
       <c r="I74">
-        <v>402</v>
+        <v>1343</v>
       </c>
       <c r="J74">
-        <v>1702</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B75">
         <v>2050</v>
@@ -3371,30 +3371,30 @@
         <v>2100</v>
       </c>
       <c r="D75">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="E75">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F75">
-        <v>838</v>
+        <v>94</v>
       </c>
       <c r="G75">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H75">
-        <v>2</v>
+        <v>1681</v>
       </c>
       <c r="I75">
-        <v>280</v>
+        <v>402</v>
       </c>
       <c r="J75">
-        <v>386</v>
+        <v>160</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B76">
         <v>2050</v>
@@ -3403,30 +3403,30 @@
         <v>2100</v>
       </c>
       <c r="D76">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="E76">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F76">
-        <v>273</v>
+        <v>838</v>
       </c>
       <c r="G76">
-        <v>272</v>
+        <v>72</v>
       </c>
       <c r="H76">
-        <v>274</v>
+        <v>2</v>
       </c>
       <c r="I76">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="J76">
-        <v>276</v>
+        <v>386</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B77">
         <v>2050</v>
@@ -3438,123 +3438,123 @@
         <v>0.95</v>
       </c>
       <c r="E77">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F77">
+        <v>273</v>
+      </c>
+      <c r="G77">
+        <v>272</v>
+      </c>
+      <c r="H77">
         <v>274</v>
       </c>
-      <c r="G77">
-        <v>17</v>
-      </c>
-      <c r="H77">
-        <v>445</v>
-      </c>
       <c r="I77">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="J77">
-        <v>177</v>
+        <v>276</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B78">
+        <v>2050</v>
+      </c>
+      <c r="C78">
         <v>2100</v>
       </c>
-      <c r="C78">
-        <v>2150</v>
-      </c>
       <c r="D78">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="E78">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F78">
+        <v>274</v>
+      </c>
+      <c r="G78">
+        <v>17</v>
+      </c>
+      <c r="H78">
         <v>445</v>
       </c>
-      <c r="G78">
-        <v>538</v>
-      </c>
-      <c r="H78">
-        <v>595</v>
-      </c>
       <c r="I78">
-        <v>357</v>
+        <v>270</v>
       </c>
       <c r="J78">
-        <v>265</v>
+        <v>177</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="B79">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="C79">
-        <v>2300</v>
+        <v>2150</v>
       </c>
       <c r="D79">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="E79">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F79">
-        <v>747</v>
+        <v>445</v>
       </c>
       <c r="G79">
-        <v>1604</v>
+        <v>538</v>
       </c>
       <c r="H79">
-        <v>283</v>
+        <v>595</v>
       </c>
       <c r="I79">
-        <v>1</v>
+        <v>357</v>
       </c>
       <c r="J79">
-        <v>14</v>
+        <v>265</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B80">
-        <v>2100</v>
+        <v>1700</v>
       </c>
       <c r="C80">
-        <v>2150</v>
+        <v>2300</v>
       </c>
       <c r="D80">
         <v>0.95</v>
       </c>
       <c r="E80">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F80">
-        <v>3</v>
+        <v>747</v>
       </c>
       <c r="G80">
-        <v>2</v>
+        <v>1604</v>
       </c>
       <c r="H80">
+        <v>283</v>
+      </c>
+      <c r="I80">
         <v>1</v>
       </c>
-      <c r="I80">
-        <v>5</v>
-      </c>
       <c r="J80">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="B81">
         <v>2100</v>
@@ -3563,30 +3563,30 @@
         <v>2150</v>
       </c>
       <c r="D81">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="E81">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F81">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="G81">
-        <v>274</v>
+        <v>2</v>
       </c>
       <c r="H81">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I81">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J81">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B82">
         <v>2100</v>
@@ -3598,59 +3598,59 @@
         <v>0.99</v>
       </c>
       <c r="E82">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F82">
-        <v>260</v>
+        <v>46</v>
       </c>
       <c r="G82">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="H82">
-        <v>258</v>
+        <v>14</v>
       </c>
       <c r="I82">
-        <v>259</v>
+        <v>1</v>
       </c>
       <c r="J82">
-        <v>257</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="B83">
-        <v>2400</v>
+        <v>2100</v>
       </c>
       <c r="C83">
-        <v>3000</v>
+        <v>2150</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="E83">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F83">
-        <v>10001</v>
+        <v>260</v>
       </c>
       <c r="G83">
-        <v>944</v>
+        <v>256</v>
       </c>
       <c r="H83">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="I83">
-        <v>996</v>
+        <v>259</v>
       </c>
       <c r="J83">
-        <v>948</v>
+        <v>257</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B84">
         <v>2400</v>
@@ -3665,24 +3665,24 @@
         <v>10</v>
       </c>
       <c r="F84">
-        <v>830</v>
+        <v>10001</v>
       </c>
       <c r="G84">
-        <v>357</v>
+        <v>944</v>
       </c>
       <c r="H84">
-        <v>595</v>
+        <v>270</v>
       </c>
       <c r="I84">
-        <v>538</v>
+        <v>996</v>
       </c>
       <c r="J84">
-        <v>1678</v>
+        <v>948</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B85">
         <v>2400</v>
@@ -3697,18 +3697,50 @@
         <v>10</v>
       </c>
       <c r="F85">
+        <v>830</v>
+      </c>
+      <c r="G85">
+        <v>357</v>
+      </c>
+      <c r="H85">
+        <v>595</v>
+      </c>
+      <c r="I85">
+        <v>538</v>
+      </c>
+      <c r="J85">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A86" t="s">
+        <v>93</v>
+      </c>
+      <c r="B86">
+        <v>2400</v>
+      </c>
+      <c r="C86">
+        <v>3000</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86">
+        <v>10</v>
+      </c>
+      <c r="F86">
         <v>1076</v>
       </c>
-      <c r="G85">
+      <c r="G86">
         <v>2</v>
       </c>
-      <c r="H85">
+      <c r="H86">
         <v>1</v>
       </c>
-      <c r="I85">
+      <c r="I86">
         <v>3</v>
       </c>
-      <c r="J85">
+      <c r="J86">
         <v>17</v>
       </c>
     </row>
